--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.37</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,88 @@
       </c>
       <c r="T2" t="n">
         <v>41.52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra x Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10.06</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.47</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -578,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.37</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AO Home Win</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -600,20 +576,6 @@
       </c>
       <c r="P2" t="n">
         <v>170</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="T2" t="n">
-        <v>41.52</v>
       </c>
     </row>
     <row r="3">
@@ -664,19 +626,15 @@
       <c r="K3" t="n">
         <v>1.47</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -686,20 +644,6 @@
       </c>
       <c r="P3" t="n">
         <v>610</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="T3" t="n">
-        <v>10.06</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-05.xlsx
@@ -561,12 +561,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -626,15 +626,19 @@
       <c r="K3" t="n">
         <v>1.47</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
